--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,6 +895,210 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125377086</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43834</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenskär, Stenskär, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>635821</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6548040</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125376886</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100279</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenskär, Stenskär, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>635809</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6548078</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,6 +1099,108 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125434543</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8436</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenskär, Stenskär, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>635772</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6548160</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125377086</v>
+        <v>125376886</v>
       </c>
       <c r="B4" t="n">
-        <v>43834</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101735</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635821</v>
+        <v>635809</v>
       </c>
       <c r="R4" t="n">
-        <v>6548040</v>
+        <v>6548078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125376886</v>
+        <v>125377086</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
+        <v>43834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>101735</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635809</v>
+        <v>635821</v>
       </c>
       <c r="R5" t="n">
-        <v>6548078</v>
+        <v>6548040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125376886</v>
+        <v>125377086</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>43932</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635809</v>
+        <v>635821</v>
       </c>
       <c r="R4" t="n">
-        <v>6548078</v>
+        <v>6548040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125377086</v>
+        <v>125376886</v>
       </c>
       <c r="B5" t="n">
-        <v>43834</v>
+        <v>100451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101735</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635821</v>
+        <v>635809</v>
       </c>
       <c r="R5" t="n">
-        <v>6548040</v>
+        <v>6548078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125377086</v>
+        <v>125376886</v>
       </c>
       <c r="B4" t="n">
-        <v>43932</v>
+        <v>100451</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101735</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635821</v>
+        <v>635809</v>
       </c>
       <c r="R4" t="n">
-        <v>6548040</v>
+        <v>6548078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125376886</v>
+        <v>125377086</v>
       </c>
       <c r="B5" t="n">
-        <v>100451</v>
+        <v>43932</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>101735</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635809</v>
+        <v>635821</v>
       </c>
       <c r="R5" t="n">
-        <v>6548078</v>
+        <v>6548040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -897,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125376886</v>
+        <v>125377086</v>
       </c>
       <c r="B4" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43933</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635809</v>
+        <v>635821</v>
       </c>
       <c r="R4" t="n">
-        <v>6548078</v>
+        <v>6548040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,15 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125377086</v>
+        <v>125376886</v>
       </c>
       <c r="B5" t="n">
-        <v>43932</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101735</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635821</v>
+        <v>635809</v>
       </c>
       <c r="R5" t="n">
-        <v>6548040</v>
+        <v>6548078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,11 +1095,6 @@
       </c>
       <c r="B6" t="n">
         <v>8436</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>125376886</v>
       </c>
       <c r="B5" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>125376886</v>
       </c>
       <c r="B5" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>125376886</v>
       </c>
       <c r="B5" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2023 artfynd.xlsx
+++ b/artfynd/A 47711-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>125376886</v>
       </c>
       <c r="B5" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
